--- a/artfynd/A 41241-2024 artfynd.xlsx
+++ b/artfynd/A 41241-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>115716</v>
       </c>
       <c r="B2" t="n">
-        <v>84985</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88965</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489564.1712189066</v>
+        <v>489564</v>
       </c>
       <c r="R2" t="n">
-        <v>6549705.132211417</v>
+        <v>6549705</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1998-08-31</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1998-08-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
